--- a/output/pdf_financials_xlsx/CDB.xlsx
+++ b/output/pdf_financials_xlsx/CDB.xlsx
@@ -1279,10 +1279,10 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-19.843682</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-21.258662</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-63.222</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-77.956</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-60.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-72.524</v>
       </c>
     </row>
     <row r="18">
@@ -1497,10 +1497,10 @@
         <v>-79.341234</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>9.921841000000001</v>
+        <v>-9.921841000000001</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.629331</v>
+        <v>-10.629331</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>31.611</v>
+        <v>-31.611</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>38.978</v>
+        <v>-38.978</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>36.262</v>
+        <v>-36.262</v>
       </c>
     </row>
     <row r="21">
@@ -1659,25 +1659,25 @@
         <v>-79.341234</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.921841000000001</v>
+        <v>-9.921841000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>10.629331</v>
+        <v>-10.629331</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-21.066</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>31.611</v>
+        <v>-31.611</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>38.978</v>
+        <v>-38.978</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>36.262</v>
+        <v>-36.262</v>
       </c>
     </row>
     <row r="24">
@@ -1853,10 +1853,10 @@
         <v>139.195147</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>248.046025</v>
+        <v>-248.046025</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>354.311033</v>
+        <v>-354.311033</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -2170,16 +2170,16 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -52640,16 +52640,16 @@
         </is>
       </c>
       <c r="P496" s="5" t="n">
-        <v>31.611</v>
+        <v>-31.611</v>
       </c>
       <c r="Q496" s="5" t="n">
-        <v>35.377</v>
+        <v>-35.377</v>
       </c>
       <c r="R496" s="5" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="S496" s="5" t="n">
-        <v>36.262</v>
+        <v>-36.262</v>
       </c>
     </row>
     <row r="497">
@@ -52973,10 +52973,10 @@
         </is>
       </c>
       <c r="M500" s="5" t="n">
-        <v>9.769956000000001</v>
+        <v>-9.769956000000001</v>
       </c>
       <c r="N500" s="5" t="n">
-        <v>10.774978</v>
+        <v>-10.774978</v>
       </c>
       <c r="O500" t="inlineStr">
         <is>
@@ -52984,16 +52984,16 @@
         </is>
       </c>
       <c r="P500" s="5" t="n">
-        <v>31.407</v>
+        <v>-31.407</v>
       </c>
       <c r="Q500" s="5" t="n">
-        <v>36.596</v>
+        <v>-36.596</v>
       </c>
       <c r="R500" s="5" t="n">
-        <v>29.705</v>
+        <v>-29.705</v>
       </c>
       <c r="S500" s="5" t="n">
-        <v>35.696</v>
+        <v>-35.696</v>
       </c>
     </row>
     <row r="501">
@@ -53238,10 +53238,10 @@
         </is>
       </c>
       <c r="M503" s="5" t="n">
-        <v>9.921841000000001</v>
+        <v>-9.921841000000001</v>
       </c>
       <c r="N503" s="5" t="n">
-        <v>10.629331</v>
+        <v>-10.629331</v>
       </c>
       <c r="O503" t="inlineStr">
         <is>
@@ -53249,16 +53249,16 @@
         </is>
       </c>
       <c r="P503" s="5" t="n">
-        <v>31.611</v>
+        <v>-31.611</v>
       </c>
       <c r="Q503" s="5" t="n">
-        <v>35.377</v>
+        <v>-35.377</v>
       </c>
       <c r="R503" s="5" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="S503" s="5" t="n">
-        <v>36.262</v>
+        <v>-36.262</v>
       </c>
     </row>
     <row r="504">
@@ -53503,10 +53503,10 @@
         </is>
       </c>
       <c r="M506" s="5" t="n">
-        <v>9.769956000000001</v>
+        <v>-9.769956000000001</v>
       </c>
       <c r="N506" s="5" t="n">
-        <v>10.774978</v>
+        <v>-10.774978</v>
       </c>
       <c r="O506" t="inlineStr">
         <is>
@@ -53514,16 +53514,16 @@
         </is>
       </c>
       <c r="P506" s="5" t="n">
-        <v>31.407</v>
+        <v>-31.407</v>
       </c>
       <c r="Q506" s="5" t="n">
-        <v>36.596</v>
+        <v>-36.596</v>
       </c>
       <c r="R506" s="5" t="n">
-        <v>29.705</v>
+        <v>-29.705</v>
       </c>
       <c r="S506" s="5" t="n">
-        <v>35.696</v>
+        <v>-35.696</v>
       </c>
     </row>
     <row r="507">
@@ -54245,10 +54245,10 @@
         </is>
       </c>
       <c r="Q514" s="5" t="n">
-        <v>38.978</v>
+        <v>-38.978</v>
       </c>
       <c r="R514" s="5" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="S514" t="inlineStr">
         <is>
@@ -54516,10 +54516,10 @@
         </is>
       </c>
       <c r="Q517" s="5" t="n">
-        <v>40.182</v>
+        <v>-40.182</v>
       </c>
       <c r="R517" s="5" t="n">
-        <v>29.705</v>
+        <v>-29.705</v>
       </c>
       <c r="S517" t="inlineStr">
         <is>
@@ -54702,10 +54702,10 @@
         </is>
       </c>
       <c r="Q519" s="5" t="n">
-        <v>38.978</v>
+        <v>-38.978</v>
       </c>
       <c r="R519" s="5" t="n">
-        <v>30.3</v>
+        <v>-30.3</v>
       </c>
       <c r="S519" t="inlineStr">
         <is>
@@ -54888,10 +54888,10 @@
         </is>
       </c>
       <c r="Q521" s="5" t="n">
-        <v>40.182</v>
+        <v>-40.182</v>
       </c>
       <c r="R521" s="5" t="n">
-        <v>29.705</v>
+        <v>-29.705</v>
       </c>
       <c r="S521" t="inlineStr">
         <is>
@@ -56322,10 +56322,10 @@
         </is>
       </c>
       <c r="M537" s="5" t="n">
-        <v>9.921841000000001</v>
+        <v>-9.921841000000001</v>
       </c>
       <c r="N537" s="5" t="n">
-        <v>10.629331</v>
+        <v>-10.629331</v>
       </c>
       <c r="O537" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CDB.xlsx
+++ b/output/pdf_financials_xlsx/CDB.xlsx
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.061725</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.116084</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.337889</v>
@@ -2308,19 +2308,19 @@
         <v>0.24716</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.477</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>10.981</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>10.981</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>14.517</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.281</v>
       </c>
     </row>
     <row r="35">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.061725</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.116084</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.337889</v>
@@ -2412,19 +2412,19 @@
         <v>0.24716</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.477</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>10.981</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>10.981</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>14.517</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.281</v>
       </c>
     </row>
     <row r="37">
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.062225</v>
+        <v>0.0005</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.136084</v>
+        <v>0.02</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.196496</v>
@@ -3036,19 +3036,19 @@
         <v>0.567593</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.498</v>
+        <v>1.021</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>12.046</v>
+        <v>1.065</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.046</v>
+        <v>1.065</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>14.917</v>
+        <v>0.4</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.973</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -52029,7 +52029,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -55902,7 +55902,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">

--- a/output/pdf_financials_xlsx/CDB.xlsx
+++ b/output/pdf_financials_xlsx/CDB.xlsx
@@ -582,10 +582,8 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
@@ -636,10 +634,8 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
@@ -690,10 +686,8 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -744,10 +738,8 @@
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
@@ -798,10 +790,8 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
@@ -852,10 +842,8 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -906,10 +894,8 @@
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
@@ -960,10 +946,8 @@
       <c r="K11" s="3" t="n">
         <v>10.557531</v>
       </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L11" s="3" t="n">
+        <v>20.329</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>29.385</v>
@@ -1014,10 +998,8 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1068,10 +1050,8 @@
       <c r="K13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>-0</v>
@@ -1122,10 +1102,8 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -1176,10 +1154,8 @@
       <c r="K15" s="3" t="n">
         <v>-0.145888</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>0.694</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>1.263</v>
@@ -1230,10 +1206,8 @@
       <c r="K16" s="3" t="n">
         <v>10.629331</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L16" s="3" t="n">
+        <v>21.066</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>31.611</v>
@@ -1258,7 +1232,7 @@
         <v>0.13272</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.672821</v>
+        <v>-0.05</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1284,10 +1258,8 @@
       <c r="K17" s="3" t="n">
         <v>-21.258662</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>-42.132</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-63.222</v>
@@ -1502,10 +1474,8 @@
       <c r="K20" s="3" t="n">
         <v>-10.629331</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-21.066</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-31.611</v>
@@ -1556,10 +1526,8 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1610,10 +1578,8 @@
       <c r="K22" s="3" t="n">
         <v>-0.201349</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -1722,15 +1688,11 @@
       <c r="K24" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L24" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.35</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -1790,15 +1752,11 @@
       <c r="K25" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L25" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0.35</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -1858,15 +1816,11 @@
       <c r="K26" s="3" t="n">
         <v>-354.311033</v>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L26" s="3" t="n">
+        <v>-72.641379</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-90.317143</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1920,10 +1874,8 @@
       <c r="K27" s="3" t="n">
         <v>10.629331</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>21.066</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>31.611</v>
@@ -1974,10 +1926,8 @@
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L28" s="3" t="n">
+        <v>0.31</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.368</v>
@@ -2028,10 +1978,8 @@
       <c r="K29" s="3" t="n">
         <v>10.629331</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>21.376</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>31.979</v>
@@ -2138,7 +2086,7 @@
         <v>-57.14285714285714</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-100</v>
+        <v>-7.431397058058533</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2164,10 +2112,8 @@
       <c r="K31" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>200</v>
@@ -7791,7 +7737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S667"/>
+  <dimension ref="A1:S678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -49279,7 +49225,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -50846,7 +50796,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E477" s="5" t="n">
         <v>-0.03318</v>
       </c>
@@ -51993,10 +51947,8 @@
       <c r="N489" s="5" t="n">
         <v>10.557531</v>
       </c>
-      <c r="O489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O489" s="5" t="n">
+        <v>20.329</v>
       </c>
       <c r="P489" s="5" t="n">
         <v>29.385</v>
@@ -52715,10 +52667,8 @@
       <c r="N497" s="5" t="n">
         <v>0.159932</v>
       </c>
-      <c r="O497" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O497" s="5" t="n">
+        <v>-0.221</v>
       </c>
       <c r="P497" s="5" t="n">
         <v>-0.319</v>
@@ -52978,10 +52928,8 @@
       <c r="N500" s="5" t="n">
         <v>-10.774978</v>
       </c>
-      <c r="O500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O500" s="5" t="n">
+        <v>-21.33</v>
       </c>
       <c r="P500" s="5" t="n">
         <v>-31.407</v>
@@ -53243,10 +53191,8 @@
       <c r="N503" s="5" t="n">
         <v>-10.629331</v>
       </c>
-      <c r="O503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O503" s="5" t="n">
+        <v>-21.066</v>
       </c>
       <c r="P503" s="5" t="n">
         <v>-31.611</v>
@@ -53508,10 +53454,8 @@
       <c r="N506" s="5" t="n">
         <v>-10.774978</v>
       </c>
-      <c r="O506" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O506" s="5" t="n">
+        <v>-21.33</v>
       </c>
       <c r="P506" s="5" t="n">
         <v>-31.407</v>
@@ -54412,15 +54356,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O516" s="5" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="P516" s="5" t="n">
+        <v>-0.204</v>
       </c>
       <c r="Q516" s="5" t="n">
         <v>1.204</v>
@@ -55324,10 +55264,8 @@
       <c r="N526" s="5" t="n">
         <v>10.427982</v>
       </c>
-      <c r="O526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O526" s="5" t="n">
+        <v>21.066</v>
       </c>
       <c r="P526" s="5" t="n">
         <v>31.611</v>
@@ -55409,10 +55347,8 @@
       <c r="N527" s="5" t="n">
         <v>10.573629</v>
       </c>
-      <c r="O527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O527" s="5" t="n">
+        <v>21.33</v>
       </c>
       <c r="P527" s="5" t="n">
         <v>31.407</v>
@@ -55498,10 +55434,8 @@
       <c r="N528" s="5" t="n">
         <v>312.626399</v>
       </c>
-      <c r="O528" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O528" s="5" t="n">
+        <v>72.279056</v>
       </c>
       <c r="P528" s="5" t="n">
         <v>89.143056</v>
@@ -55533,7 +55467,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 16 $</t>
+          <t>Exploration and evaluation expenditures 14 $</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
@@ -55577,21 +55511,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M529" s="5" t="n">
-        <v>7.58014</v>
-      </c>
-      <c r="N529" s="5" t="n">
-        <v>8.176864</v>
-      </c>
-      <c r="O529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O529" s="5" t="n">
+        <v>17.396</v>
+      </c>
+      <c r="P529" s="5" t="n">
+        <v>25.049</v>
       </c>
       <c r="Q529" t="inlineStr">
         <is>
@@ -55672,15 +55606,11 @@
       <c r="N530" s="5" t="n">
         <v>2.023356</v>
       </c>
-      <c r="O530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O530" s="5" t="n">
+        <v>2.623</v>
+      </c>
+      <c r="P530" s="5" t="n">
+        <v>3.968</v>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
@@ -55711,12 +55641,12 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Amortization 9</t>
+          <t>Depreciation 9</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -55759,21 +55689,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M531" s="5" t="n">
-        <v>0.069205</v>
-      </c>
-      <c r="N531" s="5" t="n">
-        <v>0.357311</v>
-      </c>
-      <c r="O531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O531" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P531" s="5" t="n">
+        <v>0.368</v>
       </c>
       <c r="Q531" t="inlineStr">
         <is>
@@ -55799,12 +55729,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -55852,16 +55782,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M532" s="5" t="n">
-        <v>-0.047803</v>
-      </c>
-      <c r="N532" s="5" t="n">
-        <v>-0.075185</v>
-      </c>
-      <c r="O532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O532" s="5" t="n">
+        <v>0.042</v>
       </c>
       <c r="P532" t="inlineStr">
         <is>
@@ -55892,7 +55824,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -55945,21 +55877,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M533" s="5" t="n">
-        <v>0.066371</v>
-      </c>
-      <c r="N533" s="5" t="n">
-        <v>0.217688</v>
-      </c>
-      <c r="O533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O533" s="5" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P533" s="5" t="n">
+        <v>0.963</v>
       </c>
       <c r="Q533" t="inlineStr">
         <is>
@@ -55985,12 +55917,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -56038,21 +55970,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M534" s="5" t="n">
-        <v>0.022019</v>
-      </c>
-      <c r="N534" s="5" t="n">
-        <v>-0.070703</v>
-      </c>
-      <c r="O534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O534" s="5" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="P534" s="5" t="n">
+        <v>1.263</v>
       </c>
       <c r="Q534" t="inlineStr">
         <is>
@@ -56078,7 +56010,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -56131,21 +56063,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M535" s="5" t="n">
-        <v>9.921841000000001</v>
-      </c>
-      <c r="N535" s="5" t="n">
-        <v>10.629331</v>
-      </c>
-      <c r="O535" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P535" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O535" s="5" t="n">
+        <v>21.066</v>
+      </c>
+      <c r="P535" s="5" t="n">
+        <v>31.611</v>
       </c>
       <c r="Q535" t="inlineStr">
         <is>
@@ -56171,12 +56103,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Income taxes 23</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -56268,7 +56200,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Other (income) expense</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -56321,21 +56253,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M537" s="5" t="n">
-        <v>-9.921841000000001</v>
-      </c>
-      <c r="N537" s="5" t="n">
-        <v>-10.629331</v>
-      </c>
-      <c r="O537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O537" s="5" t="n">
+        <v>-21.066</v>
+      </c>
+      <c r="P537" s="5" t="n">
+        <v>-31.611</v>
       </c>
       <c r="Q537" t="inlineStr">
         <is>
@@ -56418,15 +56350,11 @@
       <c r="N538" s="5" t="n">
         <v>-0.014285</v>
       </c>
-      <c r="O538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O538" s="5" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="P538" s="5" t="n">
+        <v>0.115</v>
       </c>
       <c r="Q538" t="inlineStr">
         <is>
@@ -56457,7 +56385,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Non-controlling interest 17</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -56510,8 +56438,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N539" s="5" t="n">
-        <v>-0.201349</v>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O539" t="inlineStr">
         <is>
@@ -56552,7 +56482,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Non-controlling interest 17</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -56605,8 +56535,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N540" s="5" t="n">
-        <v>-0.201349</v>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O540" t="inlineStr">
         <is>
@@ -56642,12 +56574,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Total comprehensive loss attributable to</t>
+          <t>Loss per share attributable to common shareholders</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Loss per share (basic and diluted) $</t>
+          <t>(basic and diluted) $</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -56695,21 +56627,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M541" s="5" t="n">
-        <v>4e-08</v>
-      </c>
-      <c r="N541" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="O541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" s="5" t="n">
+        <v>2.9e-07</v>
+      </c>
+      <c r="P541" s="5" t="n">
+        <v>3.5e-07</v>
       </c>
       <c r="Q541" t="inlineStr">
         <is>
@@ -56740,7 +56672,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 12) $</t>
+          <t>Exploration and evaluation expenditures 16 $</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
@@ -56779,16 +56711,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L542" s="5" t="n">
-        <v>76.42550900000001</v>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M542" s="5" t="n">
-        <v>7.448172</v>
-      </c>
-      <c r="N542" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.58014</v>
+      </c>
+      <c r="N542" s="5" t="n">
+        <v>8.176864</v>
       </c>
       <c r="O542" t="inlineStr">
         <is>
@@ -56829,10 +56761,14 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Corporate administration</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr"/>
+          <t>Amortization 9</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
@@ -56858,22 +56794,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J543" s="5" t="n">
-        <v>1.223512</v>
-      </c>
-      <c r="K543" s="5" t="n">
-        <v>1.56057</v>
-      </c>
-      <c r="L543" s="5" t="n">
-        <v>2.174425</v>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M543" s="5" t="n">
-        <v>1.692661</v>
-      </c>
-      <c r="N543" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.069205</v>
+      </c>
+      <c r="N543" s="5" t="n">
+        <v>0.357311</v>
       </c>
       <c r="O543" t="inlineStr">
         <is>
@@ -56909,15 +56849,19 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 11)</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -56943,22 +56887,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J544" s="5" t="n">
-        <v>0.368854</v>
-      </c>
-      <c r="K544" s="5" t="n">
-        <v>1.557084</v>
-      </c>
-      <c r="L544" s="5" t="n">
-        <v>0.687092</v>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M544" s="5" t="n">
-        <v>0.671216</v>
-      </c>
-      <c r="N544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.047803</v>
+      </c>
+      <c r="N544" s="5" t="n">
+        <v>-0.075185</v>
       </c>
       <c r="O544" t="inlineStr">
         <is>
@@ -56994,17 +56942,17 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -57032,22 +56980,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J545" s="5" t="n">
-        <v>0.073271</v>
-      </c>
-      <c r="K545" s="5" t="n">
-        <v>0.060785</v>
-      </c>
-      <c r="L545" s="5" t="n">
-        <v>0.075142</v>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M545" s="5" t="n">
-        <v>0.069205</v>
-      </c>
-      <c r="N545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066371</v>
+      </c>
+      <c r="N545" s="5" t="n">
+        <v>0.217688</v>
       </c>
       <c r="O545" t="inlineStr">
         <is>
@@ -57083,17 +57035,17 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -57121,22 +57073,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J546" s="5" t="n">
-        <v>4.843676</v>
-      </c>
-      <c r="K546" s="5" t="n">
-        <v>4.585454</v>
-      </c>
-      <c r="L546" s="5" t="n">
-        <v>79.362168</v>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M546" s="5" t="n">
-        <v>9.881254</v>
-      </c>
-      <c r="N546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022019</v>
+      </c>
+      <c r="N546" s="5" t="n">
+        <v>-0.070703</v>
       </c>
       <c r="O546" t="inlineStr">
         <is>
@@ -57172,15 +57128,19 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Interest and other (expense) income</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr"/>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -57216,16 +57176,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L547" s="5" t="n">
-        <v>0.014468</v>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M547" s="5" t="n">
-        <v>-0.018568</v>
-      </c>
-      <c r="N547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.921841000000001</v>
+      </c>
+      <c r="N547" s="5" t="n">
+        <v>10.629331</v>
       </c>
       <c r="O547" t="inlineStr">
         <is>
@@ -57261,17 +57221,17 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Income taxes 23</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -57304,14 +57264,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K548" s="5" t="n">
-        <v>-0.008635</v>
-      </c>
-      <c r="L548" s="5" t="n">
-        <v>-0.002124</v>
-      </c>
-      <c r="M548" s="5" t="n">
-        <v>-0.022019</v>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N548" t="inlineStr">
         <is>
@@ -57352,15 +57318,19 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other (income) expense</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Gain on disposition of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -57396,18 +57366,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L549" s="5" t="n">
-        <v>0.00859</v>
-      </c>
-      <c r="M549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M549" s="5" t="n">
+        <v>-9.921841000000001</v>
+      </c>
+      <c r="N549" s="5" t="n">
+        <v>-10.629331</v>
       </c>
       <c r="O549" t="inlineStr">
         <is>
@@ -57443,15 +57411,19 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Net loss attributable to</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Other income (expense) total</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr"/>
+          <t>Non-controlling interest 17</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -57477,22 +57449,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J550" s="5" t="n">
-        <v>-0.07435899999999999</v>
-      </c>
-      <c r="K550" s="5" t="n">
-        <v>0.019431</v>
-      </c>
-      <c r="L550" s="5" t="n">
-        <v>0.020934</v>
-      </c>
-      <c r="M550" s="5" t="n">
-        <v>-0.040587</v>
-      </c>
-      <c r="N550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N550" s="5" t="n">
+        <v>-0.201349</v>
       </c>
       <c r="O550" t="inlineStr">
         <is>
@@ -57528,17 +57506,17 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Total comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Non-controlling interest 17</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -57566,22 +57544,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J551" s="5" t="n">
-        <v>-4.918035</v>
-      </c>
-      <c r="K551" s="5" t="n">
-        <v>-4.566023</v>
-      </c>
-      <c r="L551" s="5" t="n">
-        <v>-79.341234</v>
-      </c>
-      <c r="M551" s="5" t="n">
-        <v>-9.921841000000001</v>
-      </c>
-      <c r="N551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N551" s="5" t="n">
+        <v>-0.201349</v>
       </c>
       <c r="O551" t="inlineStr">
         <is>
@@ -57617,15 +57601,19 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Total comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on foreign exchange translation</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr"/>
+          <t>Loss per share (basic and diluted) $</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -57661,16 +57649,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L552" s="5" t="n">
-        <v>-0.095761</v>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M552" s="5" t="n">
-        <v>0.151885</v>
-      </c>
-      <c r="N552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-08</v>
+      </c>
+      <c r="N552" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="O552" t="inlineStr">
         <is>
@@ -57706,19 +57694,15 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (Note 12) $</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -57755,10 +57739,10 @@
         </is>
       </c>
       <c r="L553" s="5" t="n">
-        <v>-79.436995</v>
+        <v>76.42550900000001</v>
       </c>
       <c r="M553" s="5" t="n">
-        <v>-9.769956000000001</v>
+        <v>7.448172</v>
       </c>
       <c r="N553" t="inlineStr">
         <is>
@@ -57799,19 +57783,15 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Corporate administration</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -57837,21 +57817,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J554" s="5" t="n">
+        <v>1.223512</v>
+      </c>
+      <c r="K554" s="5" t="n">
+        <v>1.56057</v>
       </c>
       <c r="L554" s="5" t="n">
-        <v>-5.699999999999999e-07</v>
+        <v>2.174425</v>
       </c>
       <c r="M554" s="5" t="n">
-        <v>-4e-08</v>
+        <v>1.692661</v>
       </c>
       <c r="N554" t="inlineStr">
         <is>
@@ -57892,19 +57868,15 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 11)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
@@ -57930,21 +57902,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J555" s="5" t="n">
+        <v>0.368854</v>
+      </c>
+      <c r="K555" s="5" t="n">
+        <v>1.557084</v>
       </c>
       <c r="L555" s="5" t="n">
-        <v>138.016429</v>
+        <v>0.687092</v>
       </c>
       <c r="M555" s="5" t="n">
-        <v>230.084214</v>
+        <v>0.671216</v>
       </c>
       <c r="N555" t="inlineStr">
         <is>
@@ -57990,10 +57958,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 4 and 12) $</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -58019,21 +57991,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J556" s="5" t="n">
+        <v>0.073271</v>
       </c>
       <c r="K556" s="5" t="n">
-        <v>1.407015</v>
+        <v>0.060785</v>
       </c>
       <c r="L556" s="5" t="n">
-        <v>76.42550900000001</v>
-      </c>
-      <c r="M556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.075142</v>
+      </c>
+      <c r="M556" s="5" t="n">
+        <v>0.069205</v>
       </c>
       <c r="N556" t="inlineStr">
         <is>
@@ -58079,10 +58047,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 11)</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr"/>
+          <t>Operating expenses total</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -58108,21 +58080,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J557" s="5" t="n">
+        <v>4.843676</v>
       </c>
       <c r="K557" s="5" t="n">
-        <v>1.557084</v>
+        <v>4.585454</v>
       </c>
       <c r="L557" s="5" t="n">
-        <v>0.687092</v>
-      </c>
-      <c r="M557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>79.362168</v>
+      </c>
+      <c r="M557" s="5" t="n">
+        <v>9.881254</v>
       </c>
       <c r="N557" t="inlineStr">
         <is>
@@ -58168,14 +58136,10 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest and other (expense) income</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -58201,19 +58165,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J558" s="5" t="n">
-        <v>0.03421</v>
-      </c>
-      <c r="K558" s="5" t="n">
-        <v>0.030061</v>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L558" s="5" t="n">
         <v>0.014468</v>
       </c>
-      <c r="M558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M558" s="5" t="n">
+        <v>-0.018568</v>
       </c>
       <c r="N558" t="inlineStr">
         <is>
@@ -58259,10 +58225,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Write-off of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E559" t="inlineStr">
         <is>
           <t>-</t>
@@ -58288,21 +58258,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J559" s="5" t="n">
-        <v>-0.026167</v>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K559" s="5" t="n">
-        <v>-0.001995</v>
-      </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008635</v>
+      </c>
+      <c r="L559" s="5" t="n">
+        <v>-0.002124</v>
+      </c>
+      <c r="M559" s="5" t="n">
+        <v>-0.022019</v>
       </c>
       <c r="N559" t="inlineStr">
         <is>
@@ -58343,12 +58311,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange translation</t>
+          <t>Gain on disposition of property, plant and equipment</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
@@ -58382,11 +58350,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K560" s="5" t="n">
-        <v>-0.164125</v>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L560" s="5" t="n">
-        <v>-0.095761</v>
+        <v>0.00859</v>
       </c>
       <c r="M560" t="inlineStr">
         <is>
@@ -58432,19 +58402,15 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other income (expense) total</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
@@ -58470,21 +58436,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J561" s="5" t="n">
+        <v>-0.07435899999999999</v>
       </c>
       <c r="K561" s="5" t="n">
-        <v>-4.730148</v>
+        <v>0.019431</v>
       </c>
       <c r="L561" s="5" t="n">
-        <v>-79.436995</v>
-      </c>
-      <c r="M561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020934</v>
+      </c>
+      <c r="M561" s="5" t="n">
+        <v>-0.040587</v>
       </c>
       <c r="N561" t="inlineStr">
         <is>
@@ -58525,17 +58487,17 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -58563,21 +58525,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J562" s="5" t="n">
+        <v>-4.918035</v>
       </c>
       <c r="K562" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-4.566023</v>
       </c>
       <c r="L562" s="5" t="n">
-        <v>-5.699999999999999e-07</v>
-      </c>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-79.341234</v>
+      </c>
+      <c r="M562" s="5" t="n">
+        <v>-9.921841000000001</v>
       </c>
       <c r="N562" t="inlineStr">
         <is>
@@ -58618,19 +58576,15 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -58661,16 +58615,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K563" s="5" t="n">
-        <v>85.576189</v>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L563" s="5" t="n">
-        <v>138.016429</v>
-      </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.095761</v>
+      </c>
+      <c r="M563" s="5" t="n">
+        <v>0.151885</v>
       </c>
       <c r="N563" t="inlineStr">
         <is>
@@ -58711,15 +58665,19 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 10) $</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr"/>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -58745,21 +58703,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J564" s="5" t="n">
-        <v>3.178039</v>
-      </c>
-      <c r="K564" s="5" t="n">
-        <v>1.369015</v>
-      </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L564" s="5" t="n">
+        <v>-79.436995</v>
+      </c>
+      <c r="M564" s="5" t="n">
+        <v>-9.769956000000001</v>
       </c>
       <c r="N564" t="inlineStr">
         <is>
@@ -58800,17 +58758,17 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Loss per share, basic and diluted $</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -58838,21 +58796,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J565" s="5" t="n">
-        <v>0.020631</v>
-      </c>
-      <c r="K565" s="5" t="n">
-        <v>-0.008635</v>
-      </c>
-      <c r="L565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L565" s="5" t="n">
+        <v>-5.699999999999999e-07</v>
+      </c>
+      <c r="M565" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="N565" t="inlineStr">
         <is>
@@ -58893,15 +58851,19 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Provision for amount due from related party (Note 12)</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -58927,23 +58889,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J566" s="5" t="n">
-        <v>-0.103033</v>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L566" s="5" t="n">
+        <v>138.016429</v>
+      </c>
+      <c r="M566" s="5" t="n">
+        <v>230.084214</v>
       </c>
       <c r="N566" t="inlineStr">
         <is>
@@ -58984,12 +58944,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Other comprehensive gain (loss)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange translation</t>
+          <t>Exploration and evaluation expenditures (Note 4 and 12) $</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
@@ -59018,16 +58978,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J567" s="5" t="n">
-        <v>-0.009384999999999999</v>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K567" s="5" t="n">
-        <v>-0.164125</v>
-      </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.407015</v>
+      </c>
+      <c r="L567" s="5" t="n">
+        <v>76.42550900000001</v>
       </c>
       <c r="M567" t="inlineStr">
         <is>
@@ -59073,19 +59033,15 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Other comprehensive gain (loss)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 11)</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
@@ -59111,16 +59067,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J568" s="5" t="n">
-        <v>-4.92742</v>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K568" s="5" t="n">
-        <v>-4.692148</v>
-      </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.557084</v>
+      </c>
+      <c r="L568" s="5" t="n">
+        <v>0.687092</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -59166,17 +59122,17 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Other comprehensive gain (loss)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Interest and other income</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -59205,15 +59161,13 @@
         </is>
       </c>
       <c r="J569" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.03421</v>
       </c>
       <c r="K569" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="L569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030061</v>
+      </c>
+      <c r="L569" s="5" t="n">
+        <v>0.014468</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -59259,19 +59213,15 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Other comprehensive gain (loss)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Write-off of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>
@@ -59298,10 +59248,10 @@
         </is>
       </c>
       <c r="J570" s="5" t="n">
-        <v>64.379409</v>
+        <v>-0.026167</v>
       </c>
       <c r="K570" s="5" t="n">
-        <v>85.576189</v>
+        <v>-0.001995</v>
       </c>
       <c r="L570" t="inlineStr">
         <is>
@@ -59350,10 +59300,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr"/>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>EXPLORATION EXPENDITURES (Note 8) $</t>
+          <t>Unrealized loss on foreign exchange translation</t>
         </is>
       </c>
       <c r="D571" t="inlineStr"/>
@@ -59372,26 +59326,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H571" s="5" t="n">
-        <v>1.276024</v>
-      </c>
-      <c r="I571" s="5" t="n">
-        <v>1.69932</v>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K571" s="5" t="n">
+        <v>-0.164125</v>
+      </c>
+      <c r="L571" s="5" t="n">
+        <v>-0.095761</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
@@ -59437,17 +59391,17 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -59460,29 +59414,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G572" s="5" t="n">
-        <v>0.001165</v>
-      </c>
-      <c r="H572" s="5" t="n">
-        <v>0.003051</v>
-      </c>
-      <c r="I572" s="5" t="n">
-        <v>0.01219</v>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J572" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K572" s="5" t="n">
+        <v>-4.730148</v>
+      </c>
+      <c r="L572" s="5" t="n">
+        <v>-79.436995</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
@@ -59528,17 +59484,17 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Management fees (Note 11)</t>
+          <t>Loss per share, basic and diluted $</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -59546,32 +59502,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F573" s="5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="G573" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H573" s="5" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="I573" s="5" t="n">
-        <v>0.169333</v>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K573" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="L573" s="5" t="n">
+        <v>-5.699999999999999e-07</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
@@ -59617,17 +59577,17 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Office and administration (Note 11)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -59635,32 +59595,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F574" s="5" t="n">
-        <v>0.01295</v>
-      </c>
-      <c r="G574" s="5" t="n">
-        <v>0.039026</v>
-      </c>
-      <c r="H574" s="5" t="n">
-        <v>0.135409</v>
-      </c>
-      <c r="I574" s="5" t="n">
-        <v>0.143323</v>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K574" s="5" t="n">
+        <v>85.576189</v>
+      </c>
+      <c r="L574" s="5" t="n">
+        <v>138.016429</v>
       </c>
       <c r="M574" t="inlineStr">
         <is>
@@ -59706,43 +59670,45 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E575" s="5" t="n">
-        <v>0.001284</v>
-      </c>
-      <c r="F575" s="5" t="n">
-        <v>0.021322</v>
-      </c>
-      <c r="G575" s="5" t="n">
-        <v>0.035641</v>
-      </c>
-      <c r="H575" s="5" t="n">
-        <v>0.04062</v>
-      </c>
-      <c r="I575" s="5" t="n">
-        <v>0.01901</v>
-      </c>
-      <c r="J575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation expenditures (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J575" s="5" t="n">
+        <v>3.178039</v>
+      </c>
+      <c r="K575" s="5" t="n">
+        <v>1.369015</v>
       </c>
       <c r="L575" t="inlineStr">
         <is>
@@ -59793,41 +59759,49 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Property investigation</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F576" s="5" t="n">
-        <v>0.016667</v>
-      </c>
-      <c r="G576" s="5" t="n">
-        <v>0.009488</v>
-      </c>
-      <c r="H576" s="5" t="n">
-        <v>0.041155</v>
-      </c>
-      <c r="I576" s="5" t="n">
-        <v>0.020198</v>
-      </c>
-      <c r="J576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J576" s="5" t="n">
+        <v>0.020631</v>
+      </c>
+      <c r="K576" s="5" t="n">
+        <v>-0.008635</v>
       </c>
       <c r="L576" t="inlineStr">
         <is>
@@ -59878,19 +59852,15 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Regulatory fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Provision for amount due from related party (Note 12)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -59901,19 +59871,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G577" s="5" t="n">
-        <v>0.027619</v>
-      </c>
-      <c r="H577" s="5" t="n">
-        <v>0.020716</v>
-      </c>
-      <c r="I577" s="5" t="n">
-        <v>0.020919</v>
-      </c>
-      <c r="J577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J577" s="5" t="n">
+        <v>-0.103033</v>
       </c>
       <c r="K577" t="inlineStr">
         <is>
@@ -59969,45 +59943,45 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive gain (loss)</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Salaries and benefits (Note 11)</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Unrealized loss on foreign exchange translation</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F578" s="5" t="n">
-        <v>0.035122</v>
-      </c>
-      <c r="G578" s="5" t="n">
-        <v>0.100528</v>
-      </c>
-      <c r="H578" s="5" t="n">
-        <v>0.121557</v>
-      </c>
-      <c r="I578" s="5" t="n">
-        <v>0.208549</v>
-      </c>
-      <c r="J578" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K578" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J578" s="5" t="n">
+        <v>-0.009384999999999999</v>
+      </c>
+      <c r="K578" s="5" t="n">
+        <v>-0.164125</v>
       </c>
       <c r="L578" t="inlineStr">
         <is>
@@ -60058,17 +60032,17 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive gain (loss)</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Shareholder communications (Note 11)</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -60081,24 +60055,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G579" s="5" t="n">
-        <v>0.037845</v>
-      </c>
-      <c r="H579" s="5" t="n">
-        <v>0.079473</v>
-      </c>
-      <c r="I579" s="5" t="n">
-        <v>0.059129</v>
-      </c>
-      <c r="J579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J579" s="5" t="n">
+        <v>-4.92742</v>
+      </c>
+      <c r="K579" s="5" t="n">
+        <v>-4.692148</v>
       </c>
       <c r="L579" t="inlineStr">
         <is>
@@ -60149,15 +60125,19 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive gain (loss)</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 10)</t>
-        </is>
-      </c>
-      <c r="D580" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -60168,26 +60148,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G580" s="5" t="n">
-        <v>0.026436</v>
-      </c>
-      <c r="H580" s="5" t="n">
-        <v>0.325679</v>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K580" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J580" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="K580" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="L580" t="inlineStr">
         <is>
@@ -60238,17 +60218,17 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Other comprehensive gain (loss)</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Travel (Note 11)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -60261,24 +60241,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G581" s="5" t="n">
-        <v>0.076249</v>
-      </c>
-      <c r="H581" s="5" t="n">
-        <v>0.061655</v>
-      </c>
-      <c r="I581" s="5" t="n">
-        <v>0.040969</v>
-      </c>
-      <c r="J581" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K581" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J581" s="5" t="n">
+        <v>64.379409</v>
+      </c>
+      <c r="K581" s="5" t="n">
+        <v>85.576189</v>
       </c>
       <c r="L581" t="inlineStr">
         <is>
@@ -60327,35 +60309,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
-        </is>
-      </c>
+      <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E582" s="5" t="n">
-        <v>0.017974</v>
-      </c>
-      <c r="F582" s="5" t="n">
-        <v>0.295862</v>
-      </c>
-      <c r="G582" s="5" t="n">
-        <v>0.9408570000000001</v>
+          <t>EXPLORATION EXPENDITURES (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H582" s="5" t="n">
-        <v>0.931315</v>
+        <v>1.276024</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>0.69362</v>
+        <v>1.69932</v>
       </c>
       <c r="J582" t="inlineStr">
         <is>
@@ -60421,12 +60401,12 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -60439,16 +60419,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G583" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G583" s="5" t="n">
+        <v>0.001165</v>
       </c>
       <c r="H583" s="5" t="n">
-        <v>0.011243</v>
+        <v>0.003051</v>
       </c>
       <c r="I583" s="5" t="n">
-        <v>0.041655</v>
+        <v>0.01219</v>
       </c>
       <c r="J583" t="inlineStr">
         <is>
@@ -60514,12 +60492,12 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Management fees (Note 11)</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -60527,21 +60505,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F584" s="5" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G584" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="H584" s="5" t="n">
-        <v>0.015983</v>
+        <v>0.102</v>
       </c>
       <c r="I584" s="5" t="n">
-        <v>0.290234</v>
+        <v>0.169333</v>
       </c>
       <c r="J584" t="inlineStr">
         <is>
@@ -60607,32 +60581,30 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Notes 2 and 7)</t>
-        </is>
-      </c>
-      <c r="D585" t="inlineStr"/>
+          <t>Office and administration (Note 11)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E585" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F585" s="5" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="G585" s="5" t="n">
+        <v>0.039026</v>
+      </c>
+      <c r="H585" s="5" t="n">
+        <v>0.135409</v>
       </c>
       <c r="I585" s="5" t="n">
-        <v>-1.779772</v>
+        <v>0.143323</v>
       </c>
       <c r="J585" t="inlineStr">
         <is>
@@ -60698,34 +60670,28 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E586" s="5" t="n">
+        <v>0.001284</v>
+      </c>
+      <c r="F586" s="5" t="n">
+        <v>0.021322</v>
+      </c>
+      <c r="G586" s="5" t="n">
+        <v>0.035641</v>
       </c>
       <c r="H586" s="5" t="n">
-        <v>-2.180113</v>
+        <v>0.04062</v>
       </c>
       <c r="I586" s="5" t="n">
-        <v>-3.840823</v>
+        <v>0.01901</v>
       </c>
       <c r="J586" t="inlineStr">
         <is>
@@ -60786,12 +60752,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange translation</t>
+          <t>Property investigation</t>
         </is>
       </c>
       <c r="D587" t="inlineStr"/>
@@ -60800,23 +60766,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F587" s="5" t="n">
+        <v>0.016667</v>
+      </c>
+      <c r="G587" s="5" t="n">
+        <v>0.009488</v>
+      </c>
+      <c r="H587" s="5" t="n">
+        <v>0.041155</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>-0.038359</v>
+        <v>0.020198</v>
       </c>
       <c r="J587" t="inlineStr">
         <is>
@@ -60877,17 +60837,17 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Other comprehensive gain</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Regulatory fees (Note 11)</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -60900,16 +60860,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G588" s="5" t="n">
+        <v>0.027619</v>
       </c>
       <c r="H588" s="5" t="n">
-        <v>-2.180113</v>
+        <v>0.020716</v>
       </c>
       <c r="I588" s="5" t="n">
-        <v>-3.879182</v>
+        <v>0.020919</v>
       </c>
       <c r="J588" t="inlineStr">
         <is>
@@ -60970,17 +60928,17 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted                                        $(0.21)             $(0.21)</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Salaries and benefits (Note 11)</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -60988,21 +60946,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F589" s="5" t="n">
+        <v>0.035122</v>
+      </c>
+      <c r="G589" s="5" t="n">
+        <v>0.100528</v>
       </c>
       <c r="H589" s="5" t="n">
-        <v>10.356642</v>
+        <v>0.121557</v>
       </c>
       <c r="I589" s="5" t="n">
-        <v>18.520971</v>
+        <v>0.208549</v>
       </c>
       <c r="J589" t="inlineStr">
         <is>
@@ -61063,15 +61017,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2012 8,854,712 $ 7,457,635 $ 1,421,554 $ 190,844 $ - $</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr"/>
+          <t>Shareholder communications (Note 11)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -61082,16 +61040,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G590" s="5" t="n">
+        <v>0.037845</v>
       </c>
       <c r="H590" s="5" t="n">
-        <v>6.059372</v>
+        <v>0.079473</v>
       </c>
       <c r="I590" s="5" t="n">
-        <v>-3.010661</v>
+        <v>0.059129</v>
       </c>
       <c r="J590" t="inlineStr">
         <is>
@@ -61152,19 +61108,15 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments (Note 10)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -61175,16 +61127,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G591" s="5" t="n">
+        <v>0.026436</v>
       </c>
       <c r="H591" s="5" t="n">
-        <v>-2.180113</v>
-      </c>
-      <c r="I591" s="5" t="n">
-        <v>-2.180113</v>
+        <v>0.325679</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
@@ -61245,15 +61197,19 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 4,185,556 3,072,197 694,803 - -</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr"/>
+          <t>Travel (Note 11)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -61264,18 +61220,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G592" s="5" t="n">
+        <v>0.076249</v>
       </c>
       <c r="H592" s="5" t="n">
-        <v>3.767</v>
-      </c>
-      <c r="I592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.061655</v>
+      </c>
+      <c r="I592" s="5" t="n">
+        <v>0.040969</v>
       </c>
       <c r="J592" t="inlineStr">
         <is>
@@ -61336,37 +61288,33 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Share issuance costs - (233,329) 65,248 - -</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr"/>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E593" s="5" t="n">
+        <v>0.017974</v>
+      </c>
+      <c r="F593" s="5" t="n">
+        <v>0.295862</v>
+      </c>
+      <c r="G593" s="5" t="n">
+        <v>0.9408570000000001</v>
       </c>
       <c r="H593" s="5" t="n">
-        <v>-0.168081</v>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.931315</v>
+      </c>
+      <c r="I593" s="5" t="n">
+        <v>0.69362</v>
       </c>
       <c r="J593" t="inlineStr">
         <is>
@@ -61427,15 +61375,19 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Exercise of share purchase warrants 70,592 42,356 - - -</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr"/>
+          <t>Interest and other income</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -61452,12 +61404,10 @@
         </is>
       </c>
       <c r="H594" s="5" t="n">
-        <v>0.042356</v>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011243</v>
+      </c>
+      <c r="I594" s="5" t="n">
+        <v>0.041655</v>
       </c>
       <c r="J594" t="inlineStr">
         <is>
@@ -61518,15 +61468,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Repurchase of stock options - - - (8,000) -</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -61543,12 +61497,10 @@
         </is>
       </c>
       <c r="H595" s="5" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="I595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015983</v>
+      </c>
+      <c r="I595" s="5" t="n">
+        <v>0.290234</v>
       </c>
       <c r="J595" t="inlineStr">
         <is>
@@ -61609,12 +61561,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise of warrants - 26,133 (26,133) - -</t>
+          <t>Write-down of exploration and evaluation assets (Notes 2 and 7)</t>
         </is>
       </c>
       <c r="D596" t="inlineStr"/>
@@ -61638,10 +61590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I596" s="5" t="n">
+        <v>-1.779772</v>
       </c>
       <c r="J596" t="inlineStr">
         <is>
@@ -61702,15 +61652,19 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 325,679 -</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -61727,12 +61681,10 @@
         </is>
       </c>
       <c r="H597" s="5" t="n">
-        <v>0.325679</v>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.180113</v>
+      </c>
+      <c r="I597" s="5" t="n">
+        <v>-3.840823</v>
       </c>
       <c r="J597" t="inlineStr">
         <is>
@@ -61793,12 +61745,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>Other comprehensive gain</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2013 13,110,860 10,364,992 2,155,472 508,523 -</t>
+          <t>Unrealized loss on foreign exchange translation</t>
         </is>
       </c>
       <c r="D598" t="inlineStr"/>
@@ -61817,11 +61769,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H598" s="5" t="n">
-        <v>7.838213</v>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I598" s="5" t="n">
-        <v>-5.190774</v>
+        <v>-0.038359</v>
       </c>
       <c r="J598" t="inlineStr">
         <is>
@@ -61882,12 +61836,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>Other comprehensive gain</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -61911,10 +61865,10 @@
         </is>
       </c>
       <c r="H599" s="5" t="n">
-        <v>-3.840823</v>
+        <v>-2.180113</v>
       </c>
       <c r="I599" s="5" t="n">
-        <v>-3.840823</v>
+        <v>-3.879182</v>
       </c>
       <c r="J599" t="inlineStr">
         <is>
@@ -61975,15 +61929,19 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>Loss per share, basic and diluted                                        $(0.21)             $(0.21)</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 15,000,000 9,830,908 5,169,092 - -</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -62000,12 +61958,10 @@
         </is>
       </c>
       <c r="H600" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.356642</v>
+      </c>
+      <c r="I600" s="5" t="n">
+        <v>18.520971</v>
       </c>
       <c r="J600" t="inlineStr">
         <is>
@@ -62066,12 +62022,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Shares issued for asset acquisition 27,860,580 31,761,061 - - -</t>
+          <t>Balance, April 30, 2012 8,854,712 $ 7,457,635 $ 1,421,554 $ 190,844 $ - $</t>
         </is>
       </c>
       <c r="D601" t="inlineStr"/>
@@ -62091,12 +62047,10 @@
         </is>
       </c>
       <c r="H601" s="5" t="n">
-        <v>31.761061</v>
-      </c>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.059372</v>
+      </c>
+      <c r="I601" s="5" t="n">
+        <v>-3.010661</v>
       </c>
       <c r="J601" t="inlineStr">
         <is>
@@ -62157,15 +62111,19 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Share issuance costs - (1,401,267) 633,557 - -</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
@@ -62182,12 +62140,10 @@
         </is>
       </c>
       <c r="H602" s="5" t="n">
-        <v>-0.76771</v>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.180113</v>
+      </c>
+      <c r="I602" s="5" t="n">
+        <v>-2.180113</v>
       </c>
       <c r="J602" t="inlineStr">
         <is>
@@ -62248,12 +62204,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Stock options granted upon asset acquisition - - - 56,072 -</t>
+          <t>Shares issued for private placements 4,185,556 3,072,197 694,803 - -</t>
         </is>
       </c>
       <c r="D603" t="inlineStr"/>
@@ -62273,7 +62229,7 @@
         </is>
       </c>
       <c r="H603" s="5" t="n">
-        <v>0.056072</v>
+        <v>3.767</v>
       </c>
       <c r="I603" t="inlineStr">
         <is>
@@ -62339,12 +62295,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Warrants issued upon asset acquisition - - 1,440,400 - -</t>
+          <t>Share issuance costs - (233,329) 65,248 - -</t>
         </is>
       </c>
       <c r="D604" t="inlineStr"/>
@@ -62364,7 +62320,7 @@
         </is>
       </c>
       <c r="H604" s="5" t="n">
-        <v>1.4404</v>
+        <v>-0.168081</v>
       </c>
       <c r="I604" t="inlineStr">
         <is>
@@ -62430,12 +62386,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Exercise of stock options 34,500 34,530 - - -</t>
+          <t>Exercise of share purchase warrants 70,592 42,356 - - -</t>
         </is>
       </c>
       <c r="D605" t="inlineStr"/>
@@ -62455,7 +62411,7 @@
         </is>
       </c>
       <c r="H605" s="5" t="n">
-        <v>0.03453</v>
+        <v>0.042356</v>
       </c>
       <c r="I605" t="inlineStr">
         <is>
@@ -62521,12 +62477,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise</t>
+          <t>shares    Share capital          reserve          reserve        income              Deficit              Total</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Exercise of share purchase warrants 2,806,163 2,805,005 - - -</t>
+          <t>Repurchase of stock options - - - (8,000) -</t>
         </is>
       </c>
       <c r="D606" t="inlineStr"/>
@@ -62546,7 +62502,7 @@
         </is>
       </c>
       <c r="H606" s="5" t="n">
-        <v>2.805005</v>
+        <v>-0.008</v>
       </c>
       <c r="I606" t="inlineStr">
         <is>
@@ -62612,12 +62568,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Transfer of share-based payments</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Transfer of share-based payments reserve on exercise of stock options - 31,463 - (31,463) -</t>
+          <t>Transfer of warrant reserve on exercise of warrants - 26,133 (26,133) - -</t>
         </is>
       </c>
       <c r="D607" t="inlineStr"/>
@@ -62710,7 +62666,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise of warrants - 1,130,431 (1,130,431) - -</t>
+          <t>Share-based payments - - - 325,679 -</t>
         </is>
       </c>
       <c r="D608" t="inlineStr"/>
@@ -62729,10 +62685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H608" s="5" t="n">
+        <v>0.325679</v>
       </c>
       <c r="I608" t="inlineStr">
         <is>
@@ -62803,7 +62757,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss - - - - (38,359)</t>
+          <t>Balance, April 30, 2013 13,110,860 10,364,992 2,155,472 508,523 -</t>
         </is>
       </c>
       <c r="D609" t="inlineStr"/>
@@ -62823,12 +62777,10 @@
         </is>
       </c>
       <c r="H609" s="5" t="n">
-        <v>-0.038359</v>
-      </c>
-      <c r="I609" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.838213</v>
+      </c>
+      <c r="I609" s="5" t="n">
+        <v>-5.190774</v>
       </c>
       <c r="J609" t="inlineStr">
         <is>
@@ -62894,10 +62846,14 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2014 58,812,103 $ 54,557,123 $ 8,268,090 $ 533,132 $ (38,359) $</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr"/>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E610" t="inlineStr">
         <is>
           <t>-</t>
@@ -62914,10 +62870,10 @@
         </is>
       </c>
       <c r="H610" s="5" t="n">
-        <v>54.288389</v>
+        <v>-3.840823</v>
       </c>
       <c r="I610" s="5" t="n">
-        <v>-9.031597</v>
+        <v>-3.840823</v>
       </c>
       <c r="J610" t="inlineStr">
         <is>
@@ -62976,10 +62932,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B611" t="inlineStr"/>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Transfer of warrant reserve on exercise</t>
+        </is>
+      </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>EXPLORATION EXPENDITURES (Note 7) $</t>
+          <t>Shares issued for private placements 15,000,000 9,830,908 5,169,092 - -</t>
         </is>
       </c>
       <c r="D611" t="inlineStr"/>
@@ -62988,14 +62948,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F611" s="5" t="n">
-        <v>0.376959</v>
-      </c>
-      <c r="G611" s="5" t="n">
-        <v>1.108919</v>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H611" s="5" t="n">
-        <v>1.276024</v>
+        <v>15</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -63061,12 +63025,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Finance costs (Note 8)</t>
+          <t>Shares issued for asset acquisition 27,860,580 31,761,061 - - -</t>
         </is>
       </c>
       <c r="D612" t="inlineStr"/>
@@ -63080,13 +63044,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G612" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H612" s="5" t="n">
+        <v>31.761061</v>
       </c>
       <c r="I612" t="inlineStr">
         <is>
@@ -63152,12 +63116,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Interest (Note 8)</t>
+          <t>Share issuance costs - (1,401,267) 633,557 - -</t>
         </is>
       </c>
       <c r="D613" t="inlineStr"/>
@@ -63171,13 +63135,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G613" s="5" t="n">
-        <v>0.05686</v>
-      </c>
-      <c r="H613" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H613" s="5" t="n">
+        <v>-0.76771</v>
       </c>
       <c r="I613" t="inlineStr">
         <is>
@@ -63243,19 +63207,15 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Stock options granted upon asset acquisition - - - 56,072 -</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -63266,11 +63226,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G614" s="5" t="n">
-        <v>-0.014344</v>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H614" s="5" t="n">
-        <v>0.015983</v>
+        <v>0.056072</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>
@@ -63336,12 +63298,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 6)</t>
+          <t>Warrants issued upon asset acquisition - - 1,440,400 - -</t>
         </is>
       </c>
       <c r="D615" t="inlineStr"/>
@@ -63355,13 +63317,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G615" s="5" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="n">
+        <v>1.4404</v>
       </c>
       <c r="I615" t="inlineStr">
         <is>
@@ -63427,19 +63389,15 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exercise of stock options 34,500 34,530 - - -</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr">
         <is>
           <t>-</t>
@@ -63450,11 +63408,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G616" s="5" t="n">
-        <v>-2.25512</v>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H616" s="5" t="n">
-        <v>-2.180113</v>
+        <v>0.03453</v>
       </c>
       <c r="I616" t="inlineStr">
         <is>
@@ -63520,19 +63480,15 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted                                        $(0.11)             $(0.27)</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Exercise of share purchase warrants 2,806,163 2,805,005 - - -</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
           <t>-</t>
@@ -63543,11 +63499,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G617" s="5" t="n">
-        <v>8.227593000000001</v>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H617" s="5" t="n">
-        <v>20.713283</v>
+        <v>2.805005</v>
       </c>
       <c r="I617" t="inlineStr">
         <is>
@@ -63613,12 +63571,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>Transfer of share-based payments</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2011 5,810,000 $ 893,528 $ 26,469 $ 164,408 $ - $</t>
+          <t>Transfer of share-based payments reserve on exercise of stock options - 31,463 - (31,463) -</t>
         </is>
       </c>
       <c r="D618" t="inlineStr"/>
@@ -63632,11 +63590,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G618" s="5" t="n">
-        <v>0.328864</v>
-      </c>
-      <c r="H618" s="5" t="n">
-        <v>-0.755541</v>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
@@ -63702,19 +63664,15 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Transfer of warrant reserve on exercise of warrants - 1,130,431 (1,130,431) - -</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr"/>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
@@ -63725,11 +63683,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G619" s="5" t="n">
-        <v>-2.25512</v>
-      </c>
-      <c r="H619" s="5" t="n">
-        <v>-2.25512</v>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I619" t="inlineStr">
         <is>
@@ -63795,12 +63757,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 7,042,292 4,366,785 914,934 - -</t>
+          <t>Unrealized foreign exchange loss - - - - (38,359)</t>
         </is>
       </c>
       <c r="D620" t="inlineStr"/>
@@ -63814,13 +63776,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G620" s="5" t="n">
-        <v>5.281719</v>
-      </c>
-      <c r="H620" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="n">
+        <v>-0.038359</v>
       </c>
       <c r="I620" t="inlineStr">
         <is>
@@ -63886,12 +63848,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>Transfer of warrant reserve on exercise</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component - - - - 71,429</t>
+          <t>Balance, April 30, 2014 58,812,103 $ 54,557,123 $ 8,268,090 $ 533,132 $ (38,359) $</t>
         </is>
       </c>
       <c r="D621" t="inlineStr"/>
@@ -63905,18 +63867,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G621" s="5" t="n">
-        <v>0.07142900000000001</v>
-      </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I621" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H621" s="5" t="n">
+        <v>54.288389</v>
+      </c>
+      <c r="I621" s="5" t="n">
+        <v>-9.031597</v>
       </c>
       <c r="J621" t="inlineStr">
         <is>
@@ -63975,14 +63935,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
-        </is>
-      </c>
+      <c r="B622" t="inlineStr"/>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Shares issued for convertible debentures 4,255,318 2,000,000 - - (71,429)</t>
+          <t>EXPLORATION EXPENDITURES (Note 7) $</t>
         </is>
       </c>
       <c r="D622" t="inlineStr"/>
@@ -63991,18 +63947,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F622" s="5" t="n">
+        <v>0.376959</v>
       </c>
       <c r="G622" s="5" t="n">
-        <v>1.928571</v>
-      </c>
-      <c r="H622" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.108919</v>
+      </c>
+      <c r="H622" s="5" t="n">
+        <v>1.276024</v>
       </c>
       <c r="I622" t="inlineStr">
         <is>
@@ -64068,12 +64020,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Shares issued for finance charges 600,000 500,000 - - -</t>
+          <t>Finance costs (Note 8)</t>
         </is>
       </c>
       <c r="D623" t="inlineStr"/>
@@ -64159,12 +64111,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Share issuance costs - (303,559) 80,487 - -</t>
+          <t>Interest (Note 8)</t>
         </is>
       </c>
       <c r="D624" t="inlineStr"/>
@@ -64179,7 +64131,7 @@
         </is>
       </c>
       <c r="G624" s="5" t="n">
-        <v>-0.223072</v>
+        <v>0.05686</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
@@ -64250,15 +64202,19 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Warrants issued for property acquisition - - 400,000 - -</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
@@ -64270,12 +64226,10 @@
         </is>
       </c>
       <c r="G625" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H625" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.014344</v>
+      </c>
+      <c r="H625" s="5" t="n">
+        <v>0.015983</v>
       </c>
       <c r="I625" t="inlineStr">
         <is>
@@ -64341,12 +64295,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Exercise of share purchase warrants 1,815 545 - - -</t>
+          <t>Write-off of exploration and evaluation assets (Note 6)</t>
         </is>
       </c>
       <c r="D626" t="inlineStr"/>
@@ -64361,7 +64315,7 @@
         </is>
       </c>
       <c r="G626" s="5" t="n">
-        <v>0.000545</v>
+        <v>-0.191</v>
       </c>
       <c r="H626" t="inlineStr">
         <is>
@@ -64432,15 +64386,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise of warrants - 336 (336) - -</t>
-        </is>
-      </c>
-      <c r="D627" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E627" t="inlineStr">
         <is>
           <t>-</t>
@@ -64451,15 +64409,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G627" s="5" t="n">
+        <v>-2.25512</v>
+      </c>
+      <c r="H627" s="5" t="n">
+        <v>-2.180113</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>
@@ -64525,15 +64479,19 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>Loss per share, basic and diluted                                        $(0.11)             $(0.27)</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 26,436 -</t>
-        </is>
-      </c>
-      <c r="D628" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
@@ -64545,12 +64503,10 @@
         </is>
       </c>
       <c r="G628" s="5" t="n">
-        <v>0.026436</v>
-      </c>
-      <c r="H628" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.227593000000001</v>
+      </c>
+      <c r="H628" s="5" t="n">
+        <v>20.713283</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
@@ -64616,12 +64572,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2012 17,709,425 7,457,635 1,421,554 190,844 -</t>
+          <t>Balance, April 30, 2011 5,810,000 $ 893,528 $ 26,469 $ 164,408 $ - $</t>
         </is>
       </c>
       <c r="D629" t="inlineStr"/>
@@ -64636,10 +64592,10 @@
         </is>
       </c>
       <c r="G629" s="5" t="n">
-        <v>6.059372</v>
+        <v>0.328864</v>
       </c>
       <c r="H629" s="5" t="n">
-        <v>-3.010661</v>
+        <v>-0.755541</v>
       </c>
       <c r="I629" t="inlineStr">
         <is>
@@ -64705,7 +64661,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -64729,10 +64685,10 @@
         </is>
       </c>
       <c r="G630" s="5" t="n">
-        <v>-2.180113</v>
+        <v>-2.25512</v>
       </c>
       <c r="H630" s="5" t="n">
-        <v>-2.180113</v>
+        <v>-2.25512</v>
       </c>
       <c r="I630" t="inlineStr">
         <is>
@@ -64798,12 +64754,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 8,371,112 3,072,197 694,803 - -</t>
+          <t>Shares issued for private placements 7,042,292 4,366,785 914,934 - -</t>
         </is>
       </c>
       <c r="D631" t="inlineStr"/>
@@ -64818,7 +64774,7 @@
         </is>
       </c>
       <c r="G631" s="5" t="n">
-        <v>3.767</v>
+        <v>5.281719</v>
       </c>
       <c r="H631" t="inlineStr">
         <is>
@@ -64889,12 +64845,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Share issuance costs - (233,329) 65,248 - -</t>
+          <t>Convertible debentures equity component - - - - 71,429</t>
         </is>
       </c>
       <c r="D632" t="inlineStr"/>
@@ -64909,7 +64865,7 @@
         </is>
       </c>
       <c r="G632" s="5" t="n">
-        <v>-0.168081</v>
+        <v>0.07142900000000001</v>
       </c>
       <c r="H632" t="inlineStr">
         <is>
@@ -64980,12 +64936,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Exercise of share purchase warrants 141,185 42,356 - - -</t>
+          <t>Shares issued for convertible debentures 4,255,318 2,000,000 - - (71,429)</t>
         </is>
       </c>
       <c r="D633" t="inlineStr"/>
@@ -65000,7 +64956,7 @@
         </is>
       </c>
       <c r="G633" s="5" t="n">
-        <v>0.042356</v>
+        <v>1.928571</v>
       </c>
       <c r="H633" t="inlineStr">
         <is>
@@ -65071,12 +65027,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Repurchase of stock options - - - (8,000) -</t>
+          <t>Shares issued for finance charges 600,000 500,000 - - -</t>
         </is>
       </c>
       <c r="D634" t="inlineStr"/>
@@ -65091,7 +65047,7 @@
         </is>
       </c>
       <c r="G634" s="5" t="n">
-        <v>-0.008</v>
+        <v>0.5</v>
       </c>
       <c r="H634" t="inlineStr">
         <is>
@@ -65162,12 +65118,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on exercise of warrants - 26,133 (26,133) - -</t>
+          <t>Share issuance costs - (303,559) 80,487 - -</t>
         </is>
       </c>
       <c r="D635" t="inlineStr"/>
@@ -65181,10 +65137,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G635" s="5" t="n">
+        <v>-0.223072</v>
       </c>
       <c r="H635" t="inlineStr">
         <is>
@@ -65255,12 +65209,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 325,679 -</t>
+          <t>Warrants issued for property acquisition - - 400,000 - -</t>
         </is>
       </c>
       <c r="D636" t="inlineStr"/>
@@ -65275,7 +65229,7 @@
         </is>
       </c>
       <c r="G636" s="5" t="n">
-        <v>0.325679</v>
+        <v>0.4</v>
       </c>
       <c r="H636" t="inlineStr">
         <is>
@@ -65346,12 +65300,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Transfer of warrant reserve on</t>
+          <t>shares   Share capital        reserve         reserve        reserve           Deficit           Total</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Balance, April 30, 2013 26,221,722 $ 10,364,992 $ 2,155,472 $ 508,523 $ - $</t>
+          <t>Exercise of share purchase warrants 1,815 545 - - -</t>
         </is>
       </c>
       <c r="D637" t="inlineStr"/>
@@ -65366,10 +65320,12 @@
         </is>
       </c>
       <c r="G637" s="5" t="n">
-        <v>7.838213</v>
-      </c>
-      <c r="H637" s="5" t="n">
-        <v>-5.190774</v>
+        <v>0.000545</v>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I637" t="inlineStr">
         <is>
@@ -65435,27 +65391,29 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
-        </is>
-      </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E638" s="5" t="n">
-        <v>0.000363</v>
-      </c>
-      <c r="F638" s="5" t="n">
-        <v>0.018841</v>
-      </c>
-      <c r="G638" s="5" t="n">
-        <v>0.027619</v>
+          <t>Transfer of warrant reserve on exercise of warrants - 336 (336) - -</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr"/>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H638" t="inlineStr">
         <is>
@@ -65526,29 +65484,27 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
-        </is>
-      </c>
-      <c r="D639" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payments - - - 26,436 -</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F639" s="5" t="n">
-        <v>0.001858</v>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G639" s="5" t="n">
-        <v>0.037845</v>
+        <v>0.026436</v>
       </c>
       <c r="H639" t="inlineStr">
         <is>
@@ -65619,12 +65575,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 10 and 11)</t>
+          <t>Balance, April 30, 2012 17,709,425 7,457,635 1,421,554 190,844 -</t>
         </is>
       </c>
       <c r="D640" t="inlineStr"/>
@@ -65633,16 +65589,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F640" s="5" t="n">
-        <v>0.164408</v>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G640" s="5" t="n">
-        <v>0.026436</v>
-      </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.059372</v>
+      </c>
+      <c r="H640" s="5" t="n">
+        <v>-3.010661</v>
       </c>
       <c r="I640" t="inlineStr">
         <is>
@@ -65708,17 +65664,17 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Net loss for the year - - - - -</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -65726,16 +65682,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F641" s="5" t="n">
-        <v>0.007194</v>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G641" s="5" t="n">
-        <v>0.076249</v>
-      </c>
-      <c r="H641" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.180113</v>
+      </c>
+      <c r="H641" s="5" t="n">
+        <v>-2.180113</v>
       </c>
       <c r="I641" t="inlineStr">
         <is>
@@ -65801,29 +65757,27 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for private placements 8,371,112 3,072,197 694,803 - -</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F642" s="5" t="n">
-        <v>-0.672821</v>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G642" s="5" t="n">
-        <v>-2.049776</v>
+        <v>3.767</v>
       </c>
       <c r="H642" t="inlineStr">
         <is>
@@ -65894,19 +65848,15 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (233,329) 65,248 - -</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -65918,7 +65868,7 @@
         </is>
       </c>
       <c r="G643" s="5" t="n">
-        <v>-0.014344</v>
+        <v>-0.168081</v>
       </c>
       <c r="H643" t="inlineStr">
         <is>
@@ -65989,12 +65939,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 6)</t>
+          <t>Exercise of share purchase warrants 141,185 42,356 - - -</t>
         </is>
       </c>
       <c r="D644" t="inlineStr"/>
@@ -66009,7 +65959,7 @@
         </is>
       </c>
       <c r="G644" s="5" t="n">
-        <v>-0.191</v>
+        <v>0.042356</v>
       </c>
       <c r="H644" t="inlineStr">
         <is>
@@ -66080,29 +66030,27 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Repurchase of stock options - - - (8,000) -</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F645" s="5" t="n">
-        <v>-0.672821</v>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G645" s="5" t="n">
-        <v>-2.25512</v>
+        <v>-0.008</v>
       </c>
       <c r="H645" t="inlineStr">
         <is>
@@ -66173,12 +66121,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 13)</t>
+          <t>Transfer of warrant reserve on exercise of warrants - 26,133 (26,133) - -</t>
         </is>
       </c>
       <c r="D646" t="inlineStr"/>
@@ -66187,8 +66135,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F646" s="5" t="n">
-        <v>0.05</v>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
@@ -66264,29 +66214,27 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments - - - 325,679 -</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr"/>
       <c r="E647" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F647" s="5" t="n">
-        <v>-0.622821</v>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G647" s="5" t="n">
-        <v>-2.25512</v>
+        <v>0.325679</v>
       </c>
       <c r="H647" t="inlineStr">
         <is>
@@ -66357,34 +66305,30 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted                                         $(0.27)            $(0.14)</t>
+          <t>Transfer of warrant reserve on</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Balance, April 30, 2013 26,221,722 $ 10,364,992 $ 2,155,472 $ 508,523 $ - $</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr"/>
       <c r="E648" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F648" s="5" t="n">
-        <v>4.561781</v>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G648" s="5" t="n">
-        <v>8.227593000000001</v>
-      </c>
-      <c r="H648" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.838213</v>
+      </c>
+      <c r="H648" s="5" t="n">
+        <v>-5.190774</v>
       </c>
       <c r="I648" t="inlineStr">
         <is>
@@ -66450,25 +66394,27 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Total 67,705 (622,821) 20,000 360,000 350,000 (50,000) 180,000 (140,428) 164,408 328,864 (2,255,120) 5,281,719 71,429 1,928,571 500,000 (223,072) 400,000 545 - 26,436</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E649" s="5" t="n">
+        <v>0.000363</v>
       </c>
       <c r="F649" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.018841</v>
       </c>
       <c r="G649" s="5" t="n">
-        <v>6.059372</v>
+        <v>0.027619</v>
       </c>
       <c r="H649" t="inlineStr">
         <is>
@@ -66539,27 +66485,29 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Deficit (132,720) (622,821) - - - - - - - (755,541) (2,255,120) - - - - - - - -</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr"/>
+          <t>Shareholder communications</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E650" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F650" s="5" t="n">
-        <v>-3.010661</v>
-      </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001858</v>
+      </c>
+      <c r="G650" s="5" t="n">
+        <v>0.037845</v>
       </c>
       <c r="H650" t="inlineStr">
         <is>
@@ -66630,12 +66578,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>$       to</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>- - - - - - notes 545 336Minerals capital 200,425 20,000 360,000 350,000 (50,000) 180,000 (166,897) 893,528 4,366,785 2,000,000 500,000</t>
+          <t>Share-based payments (Notes 10 and 11)</t>
         </is>
       </c>
       <c r="D651" t="inlineStr"/>
@@ -66645,10 +66593,10 @@
         </is>
       </c>
       <c r="F651" s="5" t="n">
-        <v>7.457635</v>
+        <v>0.164408</v>
       </c>
       <c r="G651" s="5" t="n">
-        <v>-0.303559</v>
+        <v>0.026436</v>
       </c>
       <c r="H651" t="inlineStr">
         <is>
@@ -66719,29 +66667,29 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>$       to</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Share accompanyingWesgold EQUITY $ - - - - - - - -</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G652" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F652" s="5" t="n">
+        <v>0.007194</v>
+      </c>
+      <c r="G652" s="5" t="n">
+        <v>0.076249</v>
       </c>
       <c r="H652" t="inlineStr">
         <is>
@@ -66812,25 +66760,29 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Year Ended October</t>
-        </is>
-      </c>
-      <c r="D653" t="inlineStr"/>
-      <c r="E653" s="5" t="n">
-        <v>0.002009</v>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F653" s="5" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="G653" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.672821</v>
+      </c>
+      <c r="G653" s="5" t="n">
+        <v>-2.049776</v>
       </c>
       <c r="H653" t="inlineStr">
         <is>
@@ -66901,25 +66853,31 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>April 30, 2011 to April</t>
-        </is>
-      </c>
-      <c r="D654" t="inlineStr"/>
-      <c r="E654" s="5" t="n">
-        <v>0.00201</v>
-      </c>
-      <c r="F654" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G654" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G654" s="5" t="n">
+        <v>-0.014344</v>
       </c>
       <c r="H654" t="inlineStr">
         <is>
@@ -66990,25 +66948,27 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>EXPLORATION EXPENDITURES (Note 5) $</t>
+          <t>Write-off of exploration and evaluation assets (Note 6)</t>
         </is>
       </c>
       <c r="D655" t="inlineStr"/>
-      <c r="E655" s="5" t="n">
-        <v>0.114746</v>
-      </c>
-      <c r="F655" s="5" t="n">
-        <v>0.376959</v>
-      </c>
-      <c r="G655" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G655" s="5" t="n">
+        <v>-0.191</v>
       </c>
       <c r="H655" t="inlineStr">
         <is>
@@ -67079,17 +67039,17 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -67098,12 +67058,10 @@
         </is>
       </c>
       <c r="F656" s="5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="G656" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.672821</v>
+      </c>
+      <c r="G656" s="5" t="n">
+        <v>-2.25512</v>
       </c>
       <c r="H656" t="inlineStr">
         <is>
@@ -67174,24 +67132,26 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office and administration (Note 7)</t>
+          <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E657" s="5" t="n">
-        <v>0.002716</v>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F657" s="5" t="n">
-        <v>0.01295</v>
+        <v>0.05</v>
       </c>
       <c r="G657" t="inlineStr">
         <is>
@@ -67267,29 +67227,29 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Salaries and wages (Note 7)</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
-      <c r="E658" s="5" t="n">
-        <v>0.013611</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F658" s="5" t="n">
-        <v>0.035122</v>
-      </c>
-      <c r="G658" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.622821</v>
+      </c>
+      <c r="G658" s="5" t="n">
+        <v>-2.25512</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
@@ -67360,27 +67320,29 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Loss per share, basic and diluted                                         $(0.27)            $(0.14)</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D659" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F659" s="5" t="n">
-        <v>0.164408</v>
-      </c>
-      <c r="G659" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.561781</v>
+      </c>
+      <c r="G659" s="5" t="n">
+        <v>8.227593000000001</v>
       </c>
       <c r="H659" t="inlineStr">
         <is>
@@ -67451,31 +67413,25 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Travel (Note 7)</t>
-        </is>
-      </c>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total 67,705 (622,821) 20,000 360,000 350,000 (50,000) 180,000 (140,428) 164,408 328,864 (2,255,120) 5,281,719 71,429 1,928,571 500,000 (223,072) 400,000 545 - 26,436</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F660" s="5" t="n">
-        <v>0.007194</v>
-      </c>
-      <c r="G660" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-06</v>
+      </c>
+      <c r="G660" s="5" t="n">
+        <v>6.059372</v>
       </c>
       <c r="H660" t="inlineStr">
         <is>
@@ -67546,24 +67502,22 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Loss for the period before income taxes</t>
-        </is>
-      </c>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E661" s="5" t="n">
-        <v>-0.13272</v>
+          <t>Deficit (132,720) (622,821) - - - - - - - (755,541) (2,255,120) - - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F661" s="5" t="n">
-        <v>-0.672821</v>
+        <v>-3.010661</v>
       </c>
       <c r="G661" t="inlineStr">
         <is>
@@ -67639,25 +67593,25 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>$       to</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Future income tax recovery (Note 9)</t>
+          <t>- - - - - - notes 545 336Minerals capital 200,425 20,000 360,000 350,000 (50,000) 180,000 (166,897) 893,528 4,366,785 2,000,000 500,000</t>
         </is>
       </c>
       <c r="D662" t="inlineStr"/>
-      <c r="E662" s="5" t="n">
-        <v>0.03318</v>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F662" s="5" t="n">
-        <v>0.093695</v>
-      </c>
-      <c r="G662" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.457635</v>
+      </c>
+      <c r="G662" s="5" t="n">
+        <v>-0.303559</v>
       </c>
       <c r="H662" t="inlineStr">
         <is>
@@ -67728,24 +67682,24 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>$       to</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period</t>
-        </is>
-      </c>
-      <c r="D663" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E663" s="5" t="n">
-        <v>-0.09954</v>
-      </c>
-      <c r="F663" s="5" t="n">
-        <v>-0.579126</v>
+          <t>Share accompanyingWesgold EQUITY $ - - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
@@ -67821,22 +67775,20 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Incorporation on</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Deficit, beginning of period</t>
+          <t>Year Ended October</t>
         </is>
       </c>
       <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E664" s="5" t="n">
+        <v>0.002009</v>
       </c>
       <c r="F664" s="5" t="n">
-        <v>-0.09954</v>
+        <v>2e-05</v>
       </c>
       <c r="G664" t="inlineStr">
         <is>
@@ -67912,20 +67864,20 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Incorporation on</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Deficit, end of period $</t>
+          <t>April 30, 2011 to April</t>
         </is>
       </c>
       <c r="D665" t="inlineStr"/>
       <c r="E665" s="5" t="n">
-        <v>-0.09954</v>
+        <v>0.00201</v>
       </c>
       <c r="F665" s="5" t="n">
-        <v>-0.678666</v>
+        <v>3e-05</v>
       </c>
       <c r="G665" t="inlineStr">
         <is>
@@ -68001,24 +67953,20 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Incorporation on</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>EXPLORATION EXPENDITURES (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr"/>
       <c r="E666" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.114746</v>
       </c>
       <c r="F666" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>0.376959</v>
       </c>
       <c r="G666" t="inlineStr">
         <is>
@@ -68094,86 +68042,1105 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F667" s="5" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Office and administration (Note 7)</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E668" s="5" t="n">
+        <v>0.002716</v>
+      </c>
+      <c r="F668" s="5" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Salaries and wages (Note 7)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
+      <c r="E669" s="5" t="n">
+        <v>0.013611</v>
+      </c>
+      <c r="F669" s="5" t="n">
+        <v>0.035122</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F670" s="5" t="n">
+        <v>0.164408</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Travel (Note 7)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F671" s="5" t="n">
+        <v>0.007194</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Loss for the period before income taxes</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E672" s="5" t="n">
+        <v>-0.13272</v>
+      </c>
+      <c r="F672" s="5" t="n">
+        <v>-0.672821</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Future income tax recovery (Note 9)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E673" s="5" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="F673" s="5" t="n">
+        <v>0.093695</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E674" s="5" t="n">
+        <v>-0.09954</v>
+      </c>
+      <c r="F674" s="5" t="n">
+        <v>-0.579126</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of period</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F675" s="5" t="n">
+        <v>-0.09954</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Deficit, end of period $</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" s="5" t="n">
+        <v>-0.09954</v>
+      </c>
+      <c r="F676" s="5" t="n">
+        <v>-0.678666</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E677" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F677" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D678" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E667" s="5" t="n">
+      <c r="E678" s="5" t="n">
         <v>2.439028</v>
       </c>
-      <c r="F667" s="5" t="n">
+      <c r="F678" s="5" t="n">
         <v>4.561781</v>
       </c>
-      <c r="G667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R667" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S667" t="inlineStr">
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
         <is>
           <t>-</t>
         </is>
